--- a/public/templates/000_pm_suite/02_프로젝트 개발/01_컨설팅/01_영업인지/프로젝트명_질의서_V1.0_20230530.xlsx
+++ b/public/templates/000_pm_suite/02_프로젝트 개발/01_컨설팅/01_영업인지/프로젝트명_질의서_V1.0_20230530.xlsx
@@ -482,7 +482,7 @@
         <sz val="10.0"/>
         <u/>
       </rPr>
-      <t>https://www.fixframe.co.kr</t>
+      <t>https://empasy.io</t>
     </r>
     <r>
       <rPr>
@@ -499,7 +499,7 @@
 감사합니다.</t>
   </si>
   <si>
-    <t>ⓒ Fixframe Inc. All rights reserved.</t>
+    <t>ⓒ Empasy Inc. All rights reserved.</t>
   </si>
   <si>
     <t>프로젝트명</t>
@@ -736,7 +736,7 @@
         <sz val="10.0"/>
         <u/>
       </rPr>
-      <t>https://www.fixframe.co.kr</t>
+      <t>https://empasy.io</t>
     </r>
     <r>
       <rPr>

--- a/public/templates/000_pm_suite/02_프로젝트 개발/01_컨설팅/01_영업인지/프로젝트명_질의서_V1.0_20230530.xlsx
+++ b/public/templates/000_pm_suite/02_프로젝트 개발/01_컨설팅/01_영업인지/프로젝트명_질의서_V1.0_20230530.xlsx
@@ -517,14 +517,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>[PM-28] 한빛글로벌 SyncGuard AI 구축 사전 요구사항 및 기술환경 질의응답서 (RFP Q&amp;A) — 주식회사 한빛글로벌 SyncGuard AI 시스템 구축</t>
+          <t>[PM-28] 한빛글로벌 SyncFlow AI 구축 사전 요구사항 및 기술환경 질의응답서 (RFP Q&amp;A) — 주식회사 한빛글로벌 SyncFlow AI 시스템 구축</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>제안 준비 및 착수 단계에서 발주처(규제심의팀·IT정보화팀)와 확인 완료한 10대 핵심 질의응답 | 발주처: 주식회사 한빛글로벌 | 수행사: 주식회사 엠파시 | 기준일: 2026.10</t>
+          <t>제안 준비 및 착수 단계에서 발주처(규제검증팀·IT정보화팀)와 확인 완료한 10대 핵심 질의응답 | 발주처: 주식회사 한빛글로벌 | 수행사: 주식회사 엠파시 | 기준일: 2026.10</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>발주처 공식 답변 (한빛글로벌 규제심의팀·IT정보화팀)</t>
+          <t>발주처 공식 답변 (한빛글로벌 규제검증팀·IT정보화팀)</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -568,17 +568,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>심의 대상 매체</t>
+          <t>검증 대상 매체</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>심의 대상 문서의 주요 파일 포맷과 페이지당 평균 용량은 어떠한가?</t>
+          <t>검증 대상 문서의 주요 파일 포맷과 페이지당 평균 용량은 어떠한가?</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>상세페이지 이미지(JPG/PNG, 최대 30MB), 브로슈어·단상자 도안 PDF(최대 80MB), 웹 입력 순수 텍스트 3종임.</t>
+          <t>기술시방서 이미지(JPG/PNG, 최대 30MB), 브로슈어·단상자 도안 PDF(최대 80MB), 웹 입력 순수 텍스트 3종임.</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>규제심의팀</t>
+          <t>규제검증팀</t>
         </is>
       </c>
     </row>
@@ -610,7 +610,7 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>표시·광고 공정화법 제3조 및 식약처 표시·광고 가이드라인 기반 100대 핵심 룰셋이며, 현업 보유 엑셀 원안을 제공함.</t>
+          <t>하도급법 제3조의4(부당특약 금지) 및 공정위·표준원 계약·기술규격 가이드라인 기반 100대 핵심 룰셋이며, 현업 보유 엑셀 원안을 제공함.</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>규제심의팀</t>
+          <t>규제검증팀</t>
         </is>
       </c>
     </row>
@@ -632,17 +632,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>전성분 데이터</t>
+          <t>자재BOM 데이터</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>ProductLab 시스템의 제품별 전성분 배합비 데이터는 어떤 방식으로 연계하는가?</t>
+          <t>PLM-Nexus 시스템의 제품별 자재BOM 조성비 데이터는 어떤 방식으로 연계하는가?</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>ProductLab DB에 읽기전용 뷰(V_AI_INGREDIENT_SPEC)를 개방하며, 매일 새벽 02:00 일배치 동기화를 권장함.</t>
+          <t>PLM-Nexus DB에 읽기전용 뷰(V_AI_INGREDIENT_SPEC)를 개방하며, 매일 새벽 02:00 일배치 동기화를 권장함.</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -664,17 +664,17 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>전성분 기밀보호</t>
+          <t>자재BOM 기밀보호</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>전성분 배합비(%) 수치를 외부 상용 LLM 프롬프트에 포함해도 무방한가?</t>
+          <t>자재BOM 조성비(%) 수치를 외부 상용 LLM 프롬프트에 포함해도 무방한가?</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>절대 불가함. 배합비 원문은 사내 DB 정규식/수치 비교 로직에서만 대조하고 외부 LLM에는 적격 여부 플래그만 전달해야 함.</t>
+          <t>절대 불가함. 조성비 원문은 사내 DB 정규식/수치 비교 로직에서만 대조하고 외부 LLM에는 적격 여부 플래그만 전달해야 함.</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>한빛글로벌 표준 HB-SSO(OAuth 2.0 / OIDC)를 사용하며 사번, 성명, 부서코드, 직급 클레임을 제공함.</t>
+          <t>한빛글로벌 표준 HB-SSO(OAuth 2.0 / OIDC)를 사용하며 사번, 성명, 부서코드, 직급 규격·계약을 제공함.</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>마케팅허브 연동</t>
+          <t>전자구매포털 연동</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>마케팅허브(MarketingHub)와 SyncGuard AI 간의 심의 흐름은?</t>
+          <t>전자구매포털(SRM-Portal)와 SyncFlow AI 간의 검증 흐름은?</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>마케팅허브에서 심의 요청 API를 호출하거나 SyncGuard AI 포털에서 직접 업로드하며, 완료 시 Webhook으로 결과를 회신함.</t>
+          <t>전자구매포털에서 검증 요청 API를 호출하거나 SyncFlow AI 포털에서 직접 업로드하며, 완료 시 Webhook으로 결과를 회신함.</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>마케팅팀</t>
+          <t>구매조달팀</t>
         </is>
       </c>
     </row>
@@ -829,12 +829,12 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>AI 심의 정확도를 최종 검수할 객관적 평가 기준은 무엇인가?</t>
+          <t>AI 검증 정확도를 최종 검수할 객관적 평가 기준은 무엇인가?</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>규제심의팀이 선정한 50대 표준 골든셋(Golden-Set) 문항에 대해 정밀도(Precision) 95% 이상, 단건 15초 이내 응답을 달성해야 함.</t>
+          <t>규제검증팀이 선정한 50대 표준 골든셋(Golden-Set) 문항에 대해 정밀도(Precision) 95% 이상, 단건 15초 이내 응답을 달성해야 함.</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>규제심의팀</t>
+          <t>규제검증팀</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>10월 중순부터 2주간 규제심의팀 및 주력 4개 브랜드(루미에르·벨르코어·아쿠아퓨어·더마쉴드) 마케터를 대상으로 실시함.</t>
+          <t>10월 중순부터 2주간 규제검증팀 및 주력 4개 사업본부(전장시스템·배터리모듈·배터리모듈본부·스마트팩토리본부) 구매담당자를 대상으로 실시함.</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
